--- a/artfynd/A 44255-2024 artfynd.xlsx
+++ b/artfynd/A 44255-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121150722</v>
+        <v>121150724</v>
       </c>
       <c r="B2" t="n">
-        <v>78598</v>
+        <v>79682</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>748646</v>
+        <v>748503</v>
       </c>
       <c r="R2" t="n">
-        <v>7301132</v>
+        <v>7301183</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -749,12 +749,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-09-26</t>
+          <t>2024-09-24</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-09-26</t>
+          <t>2024-09-24</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -789,7 +789,7 @@
         <v>121150725</v>
       </c>
       <c r="B3" t="n">
-        <v>79679</v>
+        <v>79682</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -897,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121150723</v>
+        <v>121150722</v>
       </c>
       <c r="B4" t="n">
-        <v>90973</v>
+        <v>78601</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -913,21 +913,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -941,10 +941,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>748589</v>
+        <v>748646</v>
       </c>
       <c r="R4" t="n">
-        <v>7301199</v>
+        <v>7301132</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1008,10 +1008,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121150724</v>
+        <v>121150723</v>
       </c>
       <c r="B5" t="n">
-        <v>79679</v>
+        <v>90983</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1024,21 +1024,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1052,10 +1052,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>748503</v>
+        <v>748589</v>
       </c>
       <c r="R5" t="n">
-        <v>7301183</v>
+        <v>7301199</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1082,12 +1082,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-09-24</t>
+          <t>2024-09-26</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-09-24</t>
+          <t>2024-09-26</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">

--- a/artfynd/A 44255-2024 artfynd.xlsx
+++ b/artfynd/A 44255-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121150724</v>
+        <v>121150725</v>
       </c>
       <c r="B2" t="n">
         <v>79682</v>
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>748503</v>
+        <v>748540</v>
       </c>
       <c r="R2" t="n">
-        <v>7301183</v>
+        <v>7301194</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121150725</v>
+        <v>121150722</v>
       </c>
       <c r="B3" t="n">
-        <v>79682</v>
+        <v>78601</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -802,21 +802,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -830,10 +830,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>748540</v>
+        <v>748646</v>
       </c>
       <c r="R3" t="n">
-        <v>7301194</v>
+        <v>7301132</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -860,12 +860,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-09-24</t>
+          <t>2024-09-26</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-09-24</t>
+          <t>2024-09-26</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -897,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121150722</v>
+        <v>121150724</v>
       </c>
       <c r="B4" t="n">
-        <v>78601</v>
+        <v>79682</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -913,21 +913,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -941,10 +941,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>748646</v>
+        <v>748503</v>
       </c>
       <c r="R4" t="n">
-        <v>7301132</v>
+        <v>7301183</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -971,12 +971,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-09-26</t>
+          <t>2024-09-24</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-09-26</t>
+          <t>2024-09-24</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">

--- a/artfynd/A 44255-2024 artfynd.xlsx
+++ b/artfynd/A 44255-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121150725</v>
+        <v>121150722</v>
       </c>
       <c r="B2" t="n">
-        <v>79682</v>
+        <v>78604</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>748540</v>
+        <v>748646</v>
       </c>
       <c r="R2" t="n">
-        <v>7301194</v>
+        <v>7301132</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -749,12 +749,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-09-24</t>
+          <t>2024-09-26</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-09-24</t>
+          <t>2024-09-26</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121150722</v>
+        <v>121150723</v>
       </c>
       <c r="B3" t="n">
-        <v>78601</v>
+        <v>90995</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -802,21 +802,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -830,10 +830,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>748646</v>
+        <v>748589</v>
       </c>
       <c r="R3" t="n">
-        <v>7301132</v>
+        <v>7301199</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -897,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121150724</v>
+        <v>121150725</v>
       </c>
       <c r="B4" t="n">
-        <v>79682</v>
+        <v>79685</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -941,10 +941,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>748503</v>
+        <v>748540</v>
       </c>
       <c r="R4" t="n">
-        <v>7301183</v>
+        <v>7301194</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1008,10 +1008,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121150723</v>
+        <v>121150724</v>
       </c>
       <c r="B5" t="n">
-        <v>90983</v>
+        <v>79685</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1024,21 +1024,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1052,10 +1052,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>748589</v>
+        <v>748503</v>
       </c>
       <c r="R5" t="n">
-        <v>7301199</v>
+        <v>7301183</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1082,12 +1082,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-09-26</t>
+          <t>2024-09-24</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-09-26</t>
+          <t>2024-09-24</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">

--- a/artfynd/A 44255-2024 artfynd.xlsx
+++ b/artfynd/A 44255-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121150722</v>
+        <v>121150723</v>
       </c>
       <c r="B2" t="n">
-        <v>78604</v>
+        <v>90996</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>748646</v>
+        <v>748589</v>
       </c>
       <c r="R2" t="n">
-        <v>7301132</v>
+        <v>7301199</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121150723</v>
+        <v>121150725</v>
       </c>
       <c r="B3" t="n">
-        <v>90995</v>
+        <v>79685</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -802,21 +802,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -830,10 +830,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>748589</v>
+        <v>748540</v>
       </c>
       <c r="R3" t="n">
-        <v>7301199</v>
+        <v>7301194</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -860,12 +860,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-09-26</t>
+          <t>2024-09-24</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-09-26</t>
+          <t>2024-09-24</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -897,7 +897,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121150725</v>
+        <v>121150724</v>
       </c>
       <c r="B4" t="n">
         <v>79685</v>
@@ -941,10 +941,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>748540</v>
+        <v>748503</v>
       </c>
       <c r="R4" t="n">
-        <v>7301194</v>
+        <v>7301183</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1008,10 +1008,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121150724</v>
+        <v>121150722</v>
       </c>
       <c r="B5" t="n">
-        <v>79685</v>
+        <v>78604</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1024,21 +1024,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1052,10 +1052,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>748503</v>
+        <v>748646</v>
       </c>
       <c r="R5" t="n">
-        <v>7301183</v>
+        <v>7301132</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1082,12 +1082,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-09-24</t>
+          <t>2024-09-26</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-09-24</t>
+          <t>2024-09-26</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">

--- a/artfynd/A 44255-2024 artfynd.xlsx
+++ b/artfynd/A 44255-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121150723</v>
+        <v>121150722</v>
       </c>
       <c r="B2" t="n">
-        <v>90996</v>
+        <v>78607</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>748589</v>
+        <v>748646</v>
       </c>
       <c r="R2" t="n">
-        <v>7301199</v>
+        <v>7301132</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121150725</v>
+        <v>121150724</v>
       </c>
       <c r="B3" t="n">
-        <v>79685</v>
+        <v>79688</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -830,10 +830,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>748540</v>
+        <v>748503</v>
       </c>
       <c r="R3" t="n">
-        <v>7301194</v>
+        <v>7301183</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -897,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121150724</v>
+        <v>121150723</v>
       </c>
       <c r="B4" t="n">
-        <v>79685</v>
+        <v>90999</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -913,21 +913,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -941,10 +941,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>748503</v>
+        <v>748589</v>
       </c>
       <c r="R4" t="n">
-        <v>7301183</v>
+        <v>7301199</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -971,12 +971,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-09-24</t>
+          <t>2024-09-26</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-09-24</t>
+          <t>2024-09-26</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -1008,10 +1008,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121150722</v>
+        <v>121150725</v>
       </c>
       <c r="B5" t="n">
-        <v>78604</v>
+        <v>79688</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1024,21 +1024,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1052,10 +1052,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>748646</v>
+        <v>748540</v>
       </c>
       <c r="R5" t="n">
-        <v>7301132</v>
+        <v>7301194</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1082,12 +1082,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-09-26</t>
+          <t>2024-09-24</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-09-26</t>
+          <t>2024-09-24</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">

--- a/artfynd/A 44255-2024 artfynd.xlsx
+++ b/artfynd/A 44255-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121150722</v>
+        <v>121150725</v>
       </c>
       <c r="B2" t="n">
-        <v>78607</v>
+        <v>79688</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>748646</v>
+        <v>748540</v>
       </c>
       <c r="R2" t="n">
-        <v>7301132</v>
+        <v>7301194</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -749,12 +749,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-09-26</t>
+          <t>2024-09-24</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-09-26</t>
+          <t>2024-09-24</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121150724</v>
+        <v>121150723</v>
       </c>
       <c r="B3" t="n">
-        <v>79688</v>
+        <v>90999</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -802,21 +802,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -830,10 +830,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>748503</v>
+        <v>748589</v>
       </c>
       <c r="R3" t="n">
-        <v>7301183</v>
+        <v>7301199</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -860,12 +860,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-09-24</t>
+          <t>2024-09-26</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-09-24</t>
+          <t>2024-09-26</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -897,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121150723</v>
+        <v>121150724</v>
       </c>
       <c r="B4" t="n">
-        <v>90999</v>
+        <v>79688</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -913,21 +913,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -941,10 +941,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>748589</v>
+        <v>748503</v>
       </c>
       <c r="R4" t="n">
-        <v>7301199</v>
+        <v>7301183</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -971,12 +971,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-09-26</t>
+          <t>2024-09-24</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-09-26</t>
+          <t>2024-09-24</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -1008,10 +1008,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121150725</v>
+        <v>121150722</v>
       </c>
       <c r="B5" t="n">
-        <v>79688</v>
+        <v>78607</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1024,21 +1024,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1052,10 +1052,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>748540</v>
+        <v>748646</v>
       </c>
       <c r="R5" t="n">
-        <v>7301194</v>
+        <v>7301132</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1082,12 +1082,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-09-24</t>
+          <t>2024-09-26</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-09-24</t>
+          <t>2024-09-26</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
